--- a/Excel/Excel Workbook/Excel_Data_Validation.xlsx
+++ b/Excel/Excel Workbook/Excel_Data_Validation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\My Projects\Data Projects\My Data Science Full Kit\Complete_Data_Science_Full_Course\Excel\Excel Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B445229-3D16-463E-AA10-170886E1A317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB59EE05-DB8E-4AF2-8800-BA7F01316750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>Sales_ID</t>
   </si>
@@ -153,6 +153,12 @@
   </si>
   <si>
     <t>Comments =&gt; Not more than twenty words</t>
+  </si>
+  <si>
+    <t>Sales_Time</t>
+  </si>
+  <si>
+    <t>Sales_Time =&gt; Between 9:00AM and 4:00PM</t>
   </si>
 </sst>
 </file>
@@ -188,8 +194,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="11.6328125" customWidth="1"/>
@@ -502,12 +509,12 @@
     <col min="6" max="6" width="19.36328125" customWidth="1"/>
     <col min="7" max="7" width="12.54296875" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="48" customWidth="1"/>
-    <col min="10" max="10" width="6.453125" customWidth="1"/>
-    <col min="11" max="11" width="37.90625" customWidth="1"/>
+    <col min="9" max="9" width="12.6328125" customWidth="1"/>
+    <col min="10" max="10" width="53.81640625" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -533,61 +540,86 @@
         <v>42</v>
       </c>
       <c r="I1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="I7" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="I9" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="I11" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="I13" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J13" t="s">
         <v>43</v>
       </c>
     </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J15" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Choose wisely" error="See well ooooooo... Select the right thing.............." promptTitle="List of Sales Reps" prompt="This is a list of collections of sales representatives." sqref="B2:B6" xr:uid="{5DB6F1DD-BFC0-45D1-976D-43C83B78C674}">
+      <formula1>$C$9:$C$13</formula1>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Our Sales Date" prompt="Be careful... The date is between January 1st 2026 and February 24th 2026" sqref="G2:G6" xr:uid="{4DB868C2-3A6B-4E2E-B406-0C6A42515BE4}">
+      <formula1>46023</formula1>
+      <formula2>46077</formula2>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H6" xr:uid="{9FF7C636-07E0-42F7-90BB-0FEB4C976466}">
+      <formula1>5</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
